--- a/Mediciones/RNA/L/RUN2_L_2NO.xlsx
+++ b/Mediciones/RNA/L/RUN2_L_2NO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GiHub\Resultados_Doc\Mediciones\RNA\L\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FEF35C6-0119-4987-BF42-A12216047AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C59AECC6-D42F-431F-B35D-7929B759A727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -477,6 +477,9 @@
     <t>sensors_n_now</t>
   </si>
   <si>
+    <t>RNA</t>
+  </si>
+  <si>
     <t>{
   "timestamp": "2026-07-18T21:59:15",
   "bounds": {
@@ -487,7 +490,7 @@
   },
   "serial": {
     "port": "COM7",
-    "baud": "460800",
+    "baud": "115200",
     "eol": "LF",
     "send_enabled": true
   },
@@ -578,9 +581,6 @@
   "run_id": "R20260718_215915",
   "repetition": 1
 }</t>
-  </si>
-  <si>
-    <t>RNA</t>
   </si>
 </sst>
 </file>
@@ -936,7 +936,7 @@
     </row>
     <row r="2" spans="1:1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -1041,7 +1041,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D2">
         <v>1.3530196681417981E-2</v>
@@ -1095,7 +1095,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D3">
         <v>1.3530196681417981E-2</v>
@@ -1149,7 +1149,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D4">
         <v>1.3530196681417981E-2</v>
@@ -1203,7 +1203,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D5">
         <v>1.3530196681417981E-2</v>
@@ -1257,7 +1257,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D6">
         <v>1.396493634817807E-2</v>
@@ -1311,7 +1311,7 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D7">
         <v>1.396493634817807E-2</v>
@@ -1365,7 +1365,7 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D8">
         <v>1.396493634817807E-2</v>
@@ -1419,7 +1419,7 @@
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D9">
         <v>1.396493634817807E-2</v>
@@ -1473,7 +1473,7 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D10">
         <v>1.396493634817807E-2</v>
@@ -1527,7 +1527,7 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D11">
         <v>1.396493634817807E-2</v>
@@ -1581,7 +1581,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D12">
         <v>1.396493634817807E-2</v>
@@ -1635,7 +1635,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D13">
         <v>1.396493634817807E-2</v>
@@ -1689,7 +1689,7 @@
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D14">
         <v>1.396493634817807E-2</v>
@@ -1743,7 +1743,7 @@
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D15">
         <v>1.396493634817807E-2</v>
@@ -1797,7 +1797,7 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D16">
         <v>1.559033414471174E-2</v>
@@ -1851,7 +1851,7 @@
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D17">
         <v>1.559033414471174E-2</v>
@@ -1905,7 +1905,7 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D18">
         <v>1.559033414471174E-2</v>
@@ -1959,7 +1959,7 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D19">
         <v>1.559033414471174E-2</v>
@@ -2013,7 +2013,7 @@
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D20">
         <v>1.559033414471174E-2</v>
@@ -2067,7 +2067,7 @@
         <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D21">
         <v>1.559033414471174E-2</v>
@@ -2121,7 +2121,7 @@
         <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D22">
         <v>1.559033414471174E-2</v>
@@ -2175,7 +2175,7 @@
         <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D23">
         <v>1.559033414471174E-2</v>
@@ -2229,7 +2229,7 @@
         <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D24">
         <v>1.559033414471174E-2</v>
@@ -2283,7 +2283,7 @@
         <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D25">
         <v>1.559033414471174E-2</v>
@@ -2337,7 +2337,7 @@
         <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D26">
         <v>1.559033414471174E-2</v>
@@ -2391,7 +2391,7 @@
         <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D27">
         <v>1.559033414471174E-2</v>
@@ -2445,7 +2445,7 @@
         <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D28">
         <v>1.8273972121814828E-2</v>
@@ -2499,7 +2499,7 @@
         <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D29">
         <v>1.8273972121814828E-2</v>
@@ -2553,7 +2553,7 @@
         <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D30">
         <v>1.8273972121814828E-2</v>
@@ -2607,7 +2607,7 @@
         <v>29</v>
       </c>
       <c r="C31" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D31">
         <v>1.8273972121814828E-2</v>
@@ -2661,7 +2661,7 @@
         <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D32">
         <v>1.9380170114739931E-2</v>
@@ -2715,7 +2715,7 @@
         <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D33">
         <v>1.9380170114739931E-2</v>
@@ -2769,7 +2769,7 @@
         <v>32</v>
       </c>
       <c r="C34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D34">
         <v>2.0901729379728489E-2</v>
@@ -2823,7 +2823,7 @@
         <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D35">
         <v>2.112309206505146E-2</v>
@@ -2877,7 +2877,7 @@
         <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D36">
         <v>2.7064368640245209E-2</v>
@@ -2931,7 +2931,7 @@
         <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D37">
         <v>5.463724557116173E-2</v>
@@ -2985,7 +2985,7 @@
         <v>36</v>
       </c>
       <c r="C38" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D38">
         <v>0.7902624175547015</v>
@@ -3039,7 +3039,7 @@
         <v>37</v>
       </c>
       <c r="C39" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D39">
         <v>0.91730970690744418</v>
@@ -3093,7 +3093,7 @@
         <v>38</v>
       </c>
       <c r="C40" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D40">
         <v>0.91730970690744418</v>
@@ -3147,7 +3147,7 @@
         <v>39</v>
       </c>
       <c r="C41" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D41">
         <v>0.91730970690744418</v>
@@ -3201,7 +3201,7 @@
         <v>40</v>
       </c>
       <c r="C42" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D42">
         <v>0.91730970690744418</v>
@@ -3255,7 +3255,7 @@
         <v>41</v>
       </c>
       <c r="C43" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D43">
         <v>0.91730970690744418</v>
@@ -3309,7 +3309,7 @@
         <v>42</v>
       </c>
       <c r="C44" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D44">
         <v>0.91730970690744418</v>
@@ -3363,7 +3363,7 @@
         <v>43</v>
       </c>
       <c r="C45" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D45">
         <v>0.91730970690744418</v>
@@ -3417,7 +3417,7 @@
         <v>44</v>
       </c>
       <c r="C46" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D46">
         <v>0.97661542438877391</v>
@@ -3471,7 +3471,7 @@
         <v>45</v>
       </c>
       <c r="C47" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D47">
         <v>0.97661542438877391</v>
@@ -3525,7 +3525,7 @@
         <v>46</v>
       </c>
       <c r="C48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D48">
         <v>0.97661542438877391</v>
@@ -3579,7 +3579,7 @@
         <v>47</v>
       </c>
       <c r="C49" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D49">
         <v>0.97661542438877391</v>
@@ -3633,7 +3633,7 @@
         <v>48</v>
       </c>
       <c r="C50" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D50">
         <v>0.97661542438877391</v>
@@ -3687,7 +3687,7 @@
         <v>49</v>
       </c>
       <c r="C51" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D51">
         <v>0.97661542438877391</v>
@@ -3741,7 +3741,7 @@
         <v>50</v>
       </c>
       <c r="C52" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D52">
         <v>0.97661542438877391</v>
@@ -3795,7 +3795,7 @@
         <v>51</v>
       </c>
       <c r="C53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D53">
         <v>0.97661542438877391</v>
@@ -3849,7 +3849,7 @@
         <v>52</v>
       </c>
       <c r="C54" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D54">
         <v>0.97661542438877391</v>
@@ -3903,7 +3903,7 @@
         <v>53</v>
       </c>
       <c r="C55" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D55">
         <v>0.97661542438877391</v>
@@ -3957,7 +3957,7 @@
         <v>54</v>
       </c>
       <c r="C56" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D56">
         <v>0.97661542438877391</v>
@@ -4011,7 +4011,7 @@
         <v>55</v>
       </c>
       <c r="C57" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D57">
         <v>0.97661542438877391</v>
@@ -4065,7 +4065,7 @@
         <v>56</v>
       </c>
       <c r="C58" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D58">
         <v>0.97661542438877391</v>
@@ -4119,7 +4119,7 @@
         <v>57</v>
       </c>
       <c r="C59" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D59">
         <v>0.97661542438877391</v>
@@ -4173,7 +4173,7 @@
         <v>58</v>
       </c>
       <c r="C60" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D60">
         <v>0.97661542438877391</v>
@@ -4227,7 +4227,7 @@
         <v>59</v>
       </c>
       <c r="C61" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D61">
         <v>0.97661542438877391</v>
@@ -4281,7 +4281,7 @@
         <v>60</v>
       </c>
       <c r="C62" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D62">
         <v>0.97661542438877391</v>
@@ -4335,7 +4335,7 @@
         <v>61</v>
       </c>
       <c r="C63" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D63">
         <v>0.97661542438877391</v>
@@ -4389,7 +4389,7 @@
         <v>62</v>
       </c>
       <c r="C64" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D64">
         <v>0.97661542438877391</v>
@@ -4443,7 +4443,7 @@
         <v>63</v>
       </c>
       <c r="C65" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D65">
         <v>0.97661542438877391</v>
@@ -4497,7 +4497,7 @@
         <v>64</v>
       </c>
       <c r="C66" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D66">
         <v>0.97661542438877391</v>
@@ -4551,7 +4551,7 @@
         <v>65</v>
       </c>
       <c r="C67" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D67">
         <v>0.97661542438877391</v>
@@ -4605,7 +4605,7 @@
         <v>66</v>
       </c>
       <c r="C68" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D68">
         <v>0.97661542438877391</v>
@@ -4659,7 +4659,7 @@
         <v>67</v>
       </c>
       <c r="C69" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D69">
         <v>0.97661542438877391</v>
@@ -4713,7 +4713,7 @@
         <v>68</v>
       </c>
       <c r="C70" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D70">
         <v>0.97661542438877391</v>
@@ -4767,7 +4767,7 @@
         <v>69</v>
       </c>
       <c r="C71" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D71">
         <v>0.97661542438877391</v>
@@ -4821,7 +4821,7 @@
         <v>70</v>
       </c>
       <c r="C72" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D72">
         <v>0.97661542438877391</v>
@@ -4875,7 +4875,7 @@
         <v>71</v>
       </c>
       <c r="C73" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D73">
         <v>0.97661542438877391</v>
@@ -4929,7 +4929,7 @@
         <v>72</v>
       </c>
       <c r="C74" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D74">
         <v>0.97661542438877391</v>
@@ -4983,7 +4983,7 @@
         <v>73</v>
       </c>
       <c r="C75" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D75">
         <v>0.97661542438877391</v>
@@ -5037,7 +5037,7 @@
         <v>74</v>
       </c>
       <c r="C76" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D76">
         <v>0.97661542438877391</v>
@@ -5091,7 +5091,7 @@
         <v>75</v>
       </c>
       <c r="C77" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D77">
         <v>0.97661542438877391</v>
@@ -5145,7 +5145,7 @@
         <v>76</v>
       </c>
       <c r="C78" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D78">
         <v>0.99211936069130258</v>
@@ -5199,7 +5199,7 @@
         <v>77</v>
       </c>
       <c r="C79" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D79">
         <v>0.99211936069130258</v>
@@ -5253,7 +5253,7 @@
         <v>78</v>
       </c>
       <c r="C80" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D80">
         <v>0.99211936069130258</v>
@@ -5307,7 +5307,7 @@
         <v>79</v>
       </c>
       <c r="C81" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D81">
         <v>0.99211936069130258</v>
@@ -5361,7 +5361,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D82">
         <v>0.99211936069130258</v>
@@ -5415,7 +5415,7 @@
         <v>81</v>
       </c>
       <c r="C83" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D83">
         <v>0.99211936069130258</v>
@@ -5469,7 +5469,7 @@
         <v>82</v>
       </c>
       <c r="C84" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D84">
         <v>0.99211936069130258</v>
@@ -5523,7 +5523,7 @@
         <v>83</v>
       </c>
       <c r="C85" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D85">
         <v>0.99211936069130258</v>
@@ -5577,7 +5577,7 @@
         <v>84</v>
       </c>
       <c r="C86" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D86">
         <v>0.99211936069130258</v>
@@ -5631,7 +5631,7 @@
         <v>85</v>
       </c>
       <c r="C87" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D87">
         <v>0.99211936069130258</v>
@@ -5685,7 +5685,7 @@
         <v>86</v>
       </c>
       <c r="C88" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D88">
         <v>0.99211936069130258</v>
@@ -5739,7 +5739,7 @@
         <v>87</v>
       </c>
       <c r="C89" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D89">
         <v>0.99211936069130258</v>
@@ -5793,7 +5793,7 @@
         <v>88</v>
       </c>
       <c r="C90" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D90">
         <v>0.99211936069130258</v>
@@ -5847,7 +5847,7 @@
         <v>89</v>
       </c>
       <c r="C91" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D91">
         <v>0.99211936069130258</v>
@@ -5901,7 +5901,7 @@
         <v>90</v>
       </c>
       <c r="C92" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D92">
         <v>0.99211936069130258</v>
@@ -5955,7 +5955,7 @@
         <v>91</v>
       </c>
       <c r="C93" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D93">
         <v>0.99211936069130258</v>
@@ -6009,7 +6009,7 @@
         <v>92</v>
       </c>
       <c r="C94" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D94">
         <v>0.99211936069130258</v>
@@ -6063,7 +6063,7 @@
         <v>93</v>
       </c>
       <c r="C95" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D95">
         <v>0.99211936069130258</v>
@@ -6117,7 +6117,7 @@
         <v>94</v>
       </c>
       <c r="C96" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D96">
         <v>0.99211936069130258</v>
@@ -6171,7 +6171,7 @@
         <v>95</v>
       </c>
       <c r="C97" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D97">
         <v>0.99211936069130258</v>
@@ -6225,7 +6225,7 @@
         <v>96</v>
       </c>
       <c r="C98" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D98">
         <v>0.99211936069130258</v>
@@ -6279,7 +6279,7 @@
         <v>97</v>
       </c>
       <c r="C99" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D99">
         <v>0.99211936069130258</v>
@@ -6333,7 +6333,7 @@
         <v>98</v>
       </c>
       <c r="C100" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D100">
         <v>0.99211936069130258</v>
@@ -6387,7 +6387,7 @@
         <v>99</v>
       </c>
       <c r="C101" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D101">
         <v>0.99211936069130258</v>
@@ -6441,7 +6441,7 @@
         <v>100</v>
       </c>
       <c r="C102" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D102">
         <v>0.99211936069130258</v>
@@ -6495,7 +6495,7 @@
         <v>101</v>
       </c>
       <c r="C103" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D103">
         <v>0.99211936069130258</v>
@@ -6549,7 +6549,7 @@
         <v>102</v>
       </c>
       <c r="C104" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D104">
         <v>0.99211936069130258</v>
@@ -6603,7 +6603,7 @@
         <v>103</v>
       </c>
       <c r="C105" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D105">
         <v>0.99211936069130258</v>
@@ -6657,7 +6657,7 @@
         <v>104</v>
       </c>
       <c r="C106" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D106">
         <v>0.99211936069130258</v>
@@ -6711,7 +6711,7 @@
         <v>105</v>
       </c>
       <c r="C107" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D107">
         <v>0.99211936069130258</v>
@@ -6765,7 +6765,7 @@
         <v>106</v>
       </c>
       <c r="C108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D108">
         <v>0.99211936069130258</v>
@@ -6819,7 +6819,7 @@
         <v>107</v>
       </c>
       <c r="C109" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D109">
         <v>0.99211936069130258</v>
@@ -6873,7 +6873,7 @@
         <v>108</v>
       </c>
       <c r="C110" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D110">
         <v>0.99211936069130258</v>
@@ -6927,7 +6927,7 @@
         <v>109</v>
       </c>
       <c r="C111" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D111">
         <v>0.99211936069130258</v>
@@ -6981,7 +6981,7 @@
         <v>110</v>
       </c>
       <c r="C112" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D112">
         <v>0.99211936069130258</v>
@@ -7035,7 +7035,7 @@
         <v>111</v>
       </c>
       <c r="C113" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D113">
         <v>0.99211936069130258</v>
@@ -7089,7 +7089,7 @@
         <v>112</v>
       </c>
       <c r="C114" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D114">
         <v>0.99211936069130258</v>
@@ -7143,7 +7143,7 @@
         <v>113</v>
       </c>
       <c r="C115" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D115">
         <v>0.99211936069130258</v>
@@ -7197,7 +7197,7 @@
         <v>114</v>
       </c>
       <c r="C116" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D116">
         <v>0.99211936069130258</v>
@@ -7251,7 +7251,7 @@
         <v>115</v>
       </c>
       <c r="C117" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D117">
         <v>0.99211936069130258</v>
@@ -7305,7 +7305,7 @@
         <v>116</v>
       </c>
       <c r="C118" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D118">
         <v>0.99211936069130258</v>
@@ -7359,7 +7359,7 @@
         <v>117</v>
       </c>
       <c r="C119" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D119">
         <v>0.99211936069130258</v>
@@ -7413,7 +7413,7 @@
         <v>118</v>
       </c>
       <c r="C120" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D120">
         <v>0.99211936069130258</v>
@@ -7467,7 +7467,7 @@
         <v>119</v>
       </c>
       <c r="C121" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D121">
         <v>0.99211936069130258</v>
@@ -12165,7 +12165,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
